--- a/文档资料/随从数据.xlsx
+++ b/文档资料/随从数据.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="xming">Sheet1!$B:$B</definedName>
-    <definedName name="名称">Sheet1!$B:$B</definedName>
+    <definedName name="xming">Sheet1!$C:$C</definedName>
+    <definedName name="名称">Sheet1!$C:$C</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="70">
+  <si>
+    <t>ID</t>
+  </si>
   <si>
     <t>等级</t>
   </si>
@@ -156,9 +159,6 @@
   </si>
   <si>
     <t>窜天猴</t>
-  </si>
-  <si>
-    <t>~</t>
   </si>
   <si>
     <t>对目标施加灼烧3</t>
@@ -1179,41 +1179,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1851851851852" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.37037037037037" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="8.80555555555556" style="1" customWidth="1"/>
-    <col min="9" max="9" width="44.2037037037037" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="12.8888888888889" style="1"/>
-    <col min="12" max="12" width="12.0462962962963" style="1" customWidth="1"/>
-    <col min="13" max="13" width="32.4074074074074" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1851851851852" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.37037037037037" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="8.80555555555556" style="1" customWidth="1"/>
+    <col min="10" max="10" width="44.2037037037037" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="12.8888888888889" style="1"/>
+    <col min="13" max="13" width="12.0462962962963" style="1" customWidth="1"/>
+    <col min="14" max="14" width="32.4074074074074" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2"/>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1238,10 +1238,13 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
+    <row r="2" spans="1:15">
+      <c r="A2" s="1">
+        <v>1001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>14</v>
@@ -1255,38 +1258,41 @@
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1">
-        <v>1</v>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
         <v>20</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>5</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>3</v>
       </c>
-      <c r="K2" s="1">
-        <f>H2/J2</f>
+      <c r="L2" s="1">
+        <f>I2/K2</f>
         <v>1.66666666666667</v>
       </c>
-      <c r="L2" s="1">
-        <v>1</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1">
+        <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>16</v>
@@ -1294,77 +1300,83 @@
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1">
-        <v>1</v>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
         <v>18</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>4</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>4</v>
       </c>
-      <c r="K3" s="1">
-        <f t="shared" ref="K3:K11" si="0">H3/J3</f>
-        <v>1</v>
-      </c>
       <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>20</v>
+        <f t="shared" ref="L3:L11" si="0">I3/K3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1">
+        <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>3</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="J4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1">
         <v>5</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
+    <row r="5" spans="1:15">
+      <c r="A5" s="1">
+        <v>1004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
@@ -1372,278 +1384,299 @@
       <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
         <v>12</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>5</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="J5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="1">
         <v>6</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <f t="shared" si="0"/>
         <v>0.833333333333333</v>
       </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>27</v>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
+    <row r="6" spans="1:15">
+      <c r="A6" s="1">
+        <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
         <v>30</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="J6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="1">
         <v>6</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>31</v>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
+    <row r="7" spans="1:15">
+      <c r="A7" s="1">
+        <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
         <v>10</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>3</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="J7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="1">
         <v>4</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
+    <row r="8" spans="1:15">
+      <c r="A8" s="1">
+        <v>1007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>25</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="J8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="1">
         <v>8</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
+    <row r="9" spans="1:15">
+      <c r="A9" s="1">
+        <v>1008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>50</v>
       </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
         <v>4</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="L9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>39</v>
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
+        <v>1009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>5</v>
       </c>
-      <c r="K10" s="1" t="e">
-        <f>H10/J10</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>1010</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
         <v>8</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>5</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>7.5</v>
       </c>
-      <c r="K11" s="1">
-        <f>H11/J11</f>
+      <c r="L11" s="1">
+        <f t="shared" si="0"/>
         <v>0.666666666666667</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
+        <v>1011</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>16</v>
@@ -1651,74 +1684,80 @@
       <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="1">
-        <v>1</v>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
         <v>15</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>3</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>4</v>
       </c>
-      <c r="K12" s="1">
-        <f t="shared" ref="K12:K18" si="1">H12/J12</f>
+      <c r="L12" s="1">
+        <f t="shared" ref="L12:L22" si="1">I12/K12</f>
         <v>0.75</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>1012</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="1">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>60</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>8</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>8</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
+        <v>1013</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -1726,272 +1765,293 @@
       <c r="E14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="1">
-        <v>1</v>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
         <v>14</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>2</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>2</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
+    <row r="15" spans="1:15">
+      <c r="A15" s="1">
+        <v>1014</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>12</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>3</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>5</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="L15" s="1">
-        <v>1</v>
-      </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
+    <row r="16" spans="1:15">
+      <c r="A16" s="1">
+        <v>1015</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="1">
-        <v>1</v>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
         <v>8</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>3</v>
       </c>
-      <c r="K16" s="1" t="e">
+      <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="1" t="s">
-        <v>13</v>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1">
+        <v>1016</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="1">
-        <v>1</v>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
         <v>7</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>5</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>6</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <f t="shared" si="1"/>
         <v>0.833333333333333</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1">
+        <v>1017</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
         <v>3</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>2</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>4</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="1" t="s">
-        <v>13</v>
+    <row r="19" spans="1:14">
+      <c r="A19" s="1">
+        <v>1018</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>40</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>8</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>6</v>
       </c>
-      <c r="K19" s="1">
-        <f>H19/J19</f>
+      <c r="L19" s="1">
+        <f t="shared" si="1"/>
         <v>1.33333333333333</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
+    <row r="20" spans="1:14">
+      <c r="A20" s="1">
+        <v>1019</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="1">
-        <v>1</v>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
         <v>2</v>
       </c>
-      <c r="K20" s="1">
-        <f>H20/J20</f>
+      <c r="L20" s="1">
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
+    <row r="21" spans="1:14">
+      <c r="A21" s="1">
+        <v>1020</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>16</v>
@@ -1999,77 +2059,83 @@
       <c r="E21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="1">
-        <v>1</v>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
         <v>10</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>3</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>5</v>
       </c>
-      <c r="K21" s="1">
-        <f>H21/J21</f>
+      <c r="L21" s="1">
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="1" t="s">
-        <v>13</v>
+    <row r="22" spans="1:14">
+      <c r="A22" s="1">
+        <v>1021</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="1">
-        <v>1</v>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
         <v>8</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>2</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>5</v>
       </c>
-      <c r="K22" s="1">
-        <f>H22/J22</f>
+      <c r="L22" s="1">
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
-      <c r="L22" s="1">
-        <v>1</v>
-      </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="M16:N16 A1:N1 A2 C2:N2 K3:N3 A4:N8 A9:J9 L9:N11 J10:J11 B11:G11 A3:F3 H3:I3 A10:H10 B12 D12:F12 M12:N14 D13:D15 I13 F14:F16 I15 N15" evalError="1"/>
+    <ignoredError sqref="O15 J15 G14:G16 J13 E13:E15 N12:O14 E12:G12 C12 B10:H10 I3:J3 B3:G3 C11:H11 K10:K11 M9:O11 B9:K9 B4:O8 L3:O3 D2:O2 B2 B1:O1 N16:O16" evalError="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
